--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_46.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_46.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Diligence</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>SelfConfidence</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.06064932245989468</v>
+        <v>-1.32298363850834</v>
       </c>
       <c r="C2">
-        <v>-0.7686409076435883</v>
+        <v>-1.470912002093705</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.7312191663844519</v>
+        <v>-1.192162254486417</v>
       </c>
       <c r="C3">
-        <v>-1.160521293391146</v>
+        <v>-0.7492947944879085</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.2803335245357342</v>
+        <v>0.5392729683706807</v>
       </c>
       <c r="C4">
-        <v>0.6396463224628794</v>
+        <v>-1.704976183784129</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.6971246717937848</v>
+        <v>-0.4667573153329542</v>
       </c>
       <c r="C5">
-        <v>0.55247108014045</v>
+        <v>-0.4054332001989139</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.7001769235497575</v>
+        <v>-0.2703661593689077</v>
       </c>
       <c r="C6">
-        <v>-1.725208550136462</v>
+        <v>-0.1400902384139605</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.67812692445361</v>
+        <v>0.3794060825379013</v>
       </c>
       <c r="C7">
-        <v>0.2535267382429572</v>
+        <v>-0.1223886402994253</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-1.122640468173674</v>
+        <v>-0.06362254504625862</v>
       </c>
       <c r="C8">
-        <v>-0.5761624644580169</v>
+        <v>0.1616466903495781</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-1.508877124196665</v>
+        <v>-1.280206391832447</v>
       </c>
       <c r="C9">
-        <v>-2.242943116728932</v>
+        <v>0.2665162635351346</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.9566437510077334</v>
+        <v>-0.2153275647108378</v>
       </c>
       <c r="C10">
-        <v>1.475569294521071</v>
+        <v>-0.4681886010175545</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.8808250003331315</v>
+        <v>-0.5337219494737231</v>
       </c>
       <c r="C11">
-        <v>1.253135769445106</v>
+        <v>1.165030576923385</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.3318750668008959</v>
+        <v>-0.9880892399754513</v>
       </c>
       <c r="C12">
-        <v>0.3406173143780856</v>
+        <v>-0.9132016123291891</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-1.644614093789995</v>
+        <v>-0.4403419716225851</v>
       </c>
       <c r="C13">
-        <v>-0.7326756749629768</v>
+        <v>-0.8630857849096849</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.2138560948054196</v>
+        <v>0.06795246534537554</v>
       </c>
       <c r="C14">
-        <v>-0.7122076129782883</v>
+        <v>-0.6973784539832673</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.1982009521499782</v>
+        <v>0.2103606504067686</v>
       </c>
       <c r="C15">
-        <v>-0.4700555976790827</v>
+        <v>0.4033580143051388</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.604055964928283</v>
+        <v>-2.400817393237255</v>
       </c>
       <c r="C16">
-        <v>1.346046515431917</v>
+        <v>-0.8229700347409467</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.1569422616733559</v>
+        <v>0.06957639474624905</v>
       </c>
       <c r="C17">
-        <v>0.3951305955343421</v>
+        <v>-0.3763919083263374</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.02406697322517616</v>
+        <v>0.2036072164115633</v>
       </c>
       <c r="C18">
-        <v>-1.067580716790191</v>
+        <v>-0.01481032164981583</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.08393378846254583</v>
+        <v>-0.6124667779060254</v>
       </c>
       <c r="C19">
-        <v>0.1288879696939848</v>
+        <v>-0.1125413013948647</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-1.073520873188432</v>
+        <v>-0.8669950686840003</v>
       </c>
       <c r="C20">
-        <v>-0.3113733332375087</v>
+        <v>0.7832334738160345</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>-1.190273172261023</v>
+        <v>1.525797448071338</v>
       </c>
       <c r="C21">
-        <v>-0.1613927488478071</v>
+        <v>-0.7096536564439933</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>1.026354111276896</v>
+        <v>1.331371706434258</v>
       </c>
       <c r="C22">
-        <v>0.3037529903114421</v>
+        <v>2.437449103012775</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.6854641122977307</v>
+        <v>-0.2737925045919718</v>
       </c>
       <c r="C23">
-        <v>-0.5366607140763324</v>
+        <v>-0.09931476122333616</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-1.360085533321473</v>
+        <v>0.500267877277648</v>
       </c>
       <c r="C24">
-        <v>-0.7405142966966506</v>
+        <v>0.04766023996946417</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.6734273575288293</v>
+        <v>0.3695378464796162</v>
       </c>
       <c r="C25">
-        <v>-0.02611885861794455</v>
+        <v>1.418637035501362</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-1.08344920053209</v>
+        <v>-0.7826366174473991</v>
       </c>
       <c r="C26">
-        <v>0.6476171329158269</v>
+        <v>-0.7334406464398509</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-0.227195692317726</v>
+        <v>-0.3964909124200651</v>
       </c>
       <c r="C27">
-        <v>0.504770752259194</v>
+        <v>-0.658467342983542</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.3069086514108728</v>
+        <v>0.4699156850558395</v>
       </c>
       <c r="C28">
-        <v>-0.6217742762250443</v>
+        <v>-0.02014592173249216</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.7139277357890575</v>
+        <v>0.002230051089834427</v>
       </c>
       <c r="C29">
-        <v>-1.629906927047083</v>
+        <v>-0.1226281914897427</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>1.13444603996453</v>
+        <v>1.099415629093206</v>
       </c>
       <c r="C30">
-        <v>1.405282631870674</v>
+        <v>1.834553387874412</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-1.110056350113442</v>
+        <v>-0.1109321675819915</v>
       </c>
       <c r="C31">
-        <v>0.6709039990869206</v>
+        <v>0.1981738073352103</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.6643160802497089</v>
+        <v>-0.3649417633563932</v>
       </c>
       <c r="C32">
-        <v>-0.1459830896207662</v>
+        <v>-0.686864777241764</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.8580013740432244</v>
+        <v>-1.050653119251301</v>
       </c>
       <c r="C33">
-        <v>0.7046178793636069</v>
+        <v>-0.46722433723434</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.6985559454526358</v>
+        <v>1.449164675580032</v>
       </c>
       <c r="C34">
-        <v>-0.432417491551935</v>
+        <v>1.354196583397756</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.03552124114423825</v>
+        <v>0.1582916554775705</v>
       </c>
       <c r="C35">
-        <v>-0.214554601281233</v>
+        <v>-0.09582826423435926</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.803408747620345</v>
+        <v>0.1685299562367228</v>
       </c>
       <c r="C36">
-        <v>0.02693663408005226</v>
+        <v>0.001984688334315671</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-1.771198548183669</v>
+        <v>0.3795080134487024</v>
       </c>
       <c r="C37">
-        <v>-0.7993084896950097</v>
+        <v>-0.7140488768528717</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.5878801086954002</v>
+        <v>-1.011376414372247</v>
       </c>
       <c r="C38">
-        <v>-0.3436495268927177</v>
+        <v>0.8308799958788242</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.6085223207135626</v>
+        <v>1.111873657574543</v>
       </c>
       <c r="C39">
-        <v>-1.532228489929574</v>
+        <v>0.8018490781088692</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.5058509994604757</v>
+        <v>-0.3828483395667779</v>
       </c>
       <c r="C40">
-        <v>-1.19056711842768</v>
+        <v>0.9403954309838278</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-1.997940817225901</v>
+        <v>2.311860975945646</v>
       </c>
       <c r="C41">
-        <v>-0.8759377219429546</v>
+        <v>0.672097438124467</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>2.274555622562268</v>
+        <v>0.2610491284511495</v>
       </c>
       <c r="C42">
-        <v>-0.4271363340093887</v>
+        <v>-0.3670361385409035</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.9327738245283914</v>
+        <v>1.023387394178859</v>
       </c>
       <c r="C43">
-        <v>2.270927720390407</v>
+        <v>-0.7871954506487857</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.8251660674833671</v>
+        <v>0.6072818355561734</v>
       </c>
       <c r="C44">
-        <v>-0.3009600204080453</v>
+        <v>0.0502333882978058</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.9420533083400756</v>
+        <v>1.914148934632933</v>
       </c>
       <c r="C45">
-        <v>0.7808465268454381</v>
+        <v>0.3947642496433046</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.9693607370224446</v>
+        <v>0.02527819388673256</v>
       </c>
       <c r="C46">
-        <v>-0.1601845740630352</v>
+        <v>-2.099476095054272</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.7363960047373174</v>
+        <v>0.3625754018775338</v>
       </c>
       <c r="C47">
-        <v>-0.8159456489269394</v>
+        <v>-0.1260960735237745</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.4082502233942425</v>
+        <v>-0.2884687112063415</v>
       </c>
       <c r="C48">
-        <v>-0.3376698673346589</v>
+        <v>1.050066783039619</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.7260108036153987</v>
+        <v>0.1158775355455437</v>
       </c>
       <c r="C49">
-        <v>0.3752218236929227</v>
+        <v>0.3540289491551301</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.3260251652318945</v>
+        <v>1.529460511564811</v>
       </c>
       <c r="C50">
-        <v>-0.073043711750263</v>
+        <v>1.262465751931776</v>
       </c>
     </row>
     <row r="51">
@@ -1015,660 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.5958164282664958</v>
+        <v>-0.746827515164854</v>
       </c>
       <c r="C51">
-        <v>-0.1043288391169039</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>-0.1398009288329243</v>
-      </c>
-      <c r="C52">
-        <v>-0.1384986482704833</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>-1.707453623349825</v>
-      </c>
-      <c r="C53">
-        <v>-0.280952014737685</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>0.987485249265744</v>
-      </c>
-      <c r="C54">
-        <v>1.463032320388082</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>-0.09488058070240507</v>
-      </c>
-      <c r="C55">
-        <v>-2.489036725161407</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>-1.932232809501772</v>
-      </c>
-      <c r="C56">
-        <v>-1.255847320809998</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>-0.4662387581892234</v>
-      </c>
-      <c r="C57">
-        <v>-0.5425153704807433</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>0.2625207866993841</v>
-      </c>
-      <c r="C58">
-        <v>0.3400457013682026</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>-0.454904902527643</v>
-      </c>
-      <c r="C59">
-        <v>-1.143507184156082</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>0.3548969418518663</v>
-      </c>
-      <c r="C60">
-        <v>0.5130175211427358</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>0.7760720322500326</v>
-      </c>
-      <c r="C61">
-        <v>0.1069563299914588</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>-0.2791138271412567</v>
-      </c>
-      <c r="C62">
-        <v>-1.170800028052835</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>0.6198781322159136</v>
-      </c>
-      <c r="C63">
-        <v>0.3048000606279552</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>0.285285142592156</v>
-      </c>
-      <c r="C64">
-        <v>-0.2003315091461761</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>0.4765221179789939</v>
-      </c>
-      <c r="C65">
-        <v>-0.3995833897024502</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>0.7636528616725663</v>
-      </c>
-      <c r="C66">
-        <v>-1.510789595719709</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>1.119771829705564</v>
-      </c>
-      <c r="C67">
-        <v>0.6683984815293444</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>-2.423151601177152</v>
-      </c>
-      <c r="C68">
-        <v>-2.416264383932138</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>-1.381986084613385</v>
-      </c>
-      <c r="C69">
-        <v>0.9953995894590294</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>-0.5137608191924339</v>
-      </c>
-      <c r="C70">
-        <v>0.4103206191999635</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>0.4138849725439196</v>
-      </c>
-      <c r="C71">
-        <v>0.3190293471482719</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>-0.4657324140702417</v>
-      </c>
-      <c r="C72">
-        <v>-0.1957977629732468</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>-0.8950975043699674</v>
-      </c>
-      <c r="C73">
-        <v>0.1401787127946289</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>-1.129760930672715</v>
-      </c>
-      <c r="C74">
-        <v>-0.05925786823470564</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>1.907313604948783</v>
-      </c>
-      <c r="C75">
-        <v>1.504316119600137</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>0.4937979771328494</v>
-      </c>
-      <c r="C76">
-        <v>0.676232147278509</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>-0.04246076692928662</v>
-      </c>
-      <c r="C77">
-        <v>0.75768175123377</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>0.115533811691393</v>
-      </c>
-      <c r="C78">
-        <v>-0.171669966293079</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>0.1113173333556274</v>
-      </c>
-      <c r="C79">
-        <v>-1.720269510240126</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>2.062044543834556</v>
-      </c>
-      <c r="C80">
-        <v>1.831245965889588</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>0.7329642902503832</v>
-      </c>
-      <c r="C81">
-        <v>1.502340006034078</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>-1.127193287111062</v>
-      </c>
-      <c r="C82">
-        <v>0.2262078522591391</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>-1.197836225091828</v>
-      </c>
-      <c r="C83">
-        <v>0.3179113759913549</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>-0.8304239796782192</v>
-      </c>
-      <c r="C84">
-        <v>-0.5069112998645191</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>0.01060447869669845</v>
-      </c>
-      <c r="C85">
-        <v>-0.5350717933553706</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>-1.30226278496225</v>
-      </c>
-      <c r="C86">
-        <v>-0.5603998575025015</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>0.3711729910298924</v>
-      </c>
-      <c r="C87">
-        <v>-0.3908411169490876</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>0.4319718728851612</v>
-      </c>
-      <c r="C88">
-        <v>0.4697333483240791</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>-1.110933075720872</v>
-      </c>
-      <c r="C89">
-        <v>0.4129395525146283</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>0.9214157370905598</v>
-      </c>
-      <c r="C90">
-        <v>0.4947740901687989</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>1.485498297748678</v>
-      </c>
-      <c r="C91">
-        <v>0.5005227877956163</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>0.1427986206678719</v>
-      </c>
-      <c r="C92">
-        <v>0.5824429808773686</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>0.8357173238446876</v>
-      </c>
-      <c r="C93">
-        <v>0.7975419664606718</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>1.467105864414149</v>
-      </c>
-      <c r="C94">
-        <v>1.286960765468497</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>-0.6525738307471709</v>
-      </c>
-      <c r="C95">
-        <v>-0.1892747157170263</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>-0.6889209548750643</v>
-      </c>
-      <c r="C96">
-        <v>-2.279492111180542</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>0.5056371435849578</v>
-      </c>
-      <c r="C97">
-        <v>0.2069504938825479</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>-0.2367841829087756</v>
-      </c>
-      <c r="C98">
-        <v>0.360873185007243</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>0.6807154384683892</v>
-      </c>
-      <c r="C99">
-        <v>1.293128771123498</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>-0.6963653746548332</v>
-      </c>
-      <c r="C100">
-        <v>-1.160113530725786</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>1.005673157255145</v>
-      </c>
-      <c r="C101">
-        <v>1.12402779884786</v>
+        <v>0.225572859322797</v>
       </c>
     </row>
   </sheetData>
